--- a/.storybook/public/audits/SyCheckbox.xlsx
+++ b/.storybook/public/audits/SyCheckbox.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CHARRIER-32221\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\charrier-32221\design-system-v3\.storybook\public\audits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{256C65E3-4EA7-44F7-91DB-B570F599E897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A791B9-3CE9-481D-BE82-977C3524DA5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="SyCheckbox" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="290">
   <si>
     <t>Thématique</t>
   </si>
@@ -1073,6 +1072,9 @@
   </si>
   <si>
     <t>1.1.2</t>
+  </si>
+  <si>
+    <t>Correction post audit V1 - (voir - https://github.com/assurance-maladie-digital/design-system-v3/pull/2366)</t>
   </si>
 </sst>
 </file>
@@ -1373,7 +1375,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1418,23 +1420,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -1454,32 +1456,35 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1985,30 +1990,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="38" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" spans="1:6" ht="18">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="42" t="s">
         <v>242</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
       <c r="D2" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="E2" s="18"/>
+      <c r="E2" s="43" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="18">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
       <c r="D3" s="8">
         <v>45945</v>
       </c>
@@ -2017,24 +2024,24 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="26"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="41"/>
       <c r="D4" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="24" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16.05" customHeight="1">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="36" t="s">
         <v>230</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
       <c r="D5" s="9">
         <f xml:space="preserve"> COUNTIF($D$14:$D$119,"Conforme")</f>
         <v>11</v>
@@ -2044,11 +2051,11 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="18">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="36" t="s">
         <v>231</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
       <c r="D6" s="9">
         <f xml:space="preserve"> COUNTIF($D$14:$D$119,"Non conforme")</f>
         <v>8</v>
@@ -2058,11 +2065,11 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="18">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="36" t="s">
         <v>237</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
       <c r="D7" s="9">
         <f xml:space="preserve"> COUNTIF($D$14:$D$119,"Non applicable")</f>
         <v>87</v>
@@ -2072,11 +2079,11 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="18">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="36" t="s">
         <v>232</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
       <c r="D8" s="9">
         <f xml:space="preserve"> COUNTIF($D$14:$D$119,"Dérogé")</f>
         <v>0</v>
@@ -2086,11 +2093,11 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="18">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
       <c r="D9" s="9">
         <f xml:space="preserve"> COUNTIF($D$14:$D$119,"Non testé")</f>
         <v>0</v>
@@ -2153,7 +2160,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="18">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="37" t="s">
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -2182,7 +2189,7 @@
       <c r="E15" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="22" t="s">
         <v>280</v>
       </c>
     </row>
@@ -2360,7 +2367,7 @@
       <c r="E27" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="F27" s="40" t="s">
+      <c r="F27" s="22" t="s">
         <v>281</v>
       </c>
     </row>
@@ -2708,7 +2715,7 @@
       <c r="E51" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="F51" s="41" t="s">
+      <c r="F51" s="23" t="s">
         <v>282</v>
       </c>
     </row>
@@ -2740,7 +2747,7 @@
       <c r="E53" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="F53" s="40" t="s">
+      <c r="F53" s="22" t="s">
         <v>287</v>
       </c>
     </row>
@@ -2802,7 +2809,7 @@
       <c r="E57" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="F57" s="40" t="s">
+      <c r="F57" s="22" t="s">
         <v>283</v>
       </c>
     </row>
@@ -2962,7 +2969,7 @@
       <c r="E68" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="F68" s="40" t="s">
+      <c r="F68" s="22" t="s">
         <v>286</v>
       </c>
     </row>
@@ -3088,7 +3095,7 @@
       <c r="E76" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="F76" s="40" t="s">
+      <c r="F76" s="22" t="s">
         <v>281</v>
       </c>
     </row>
@@ -3344,7 +3351,7 @@
       <c r="E93" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="F93" s="40" t="s">
+      <c r="F93" s="22" t="s">
         <v>285</v>
       </c>
     </row>
@@ -3726,73 +3733,87 @@
       <c r="D120" s="5"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="A123" s="38" t="s">
+      <c r="A123" s="34" t="s">
         <v>235</v>
       </c>
-      <c r="B123" s="38"/>
-      <c r="C123" s="38"/>
-      <c r="D123" s="38"/>
+      <c r="B123" s="34"/>
+      <c r="C123" s="34"/>
+      <c r="D123" s="34"/>
       <c r="E123" s="10" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="259.05" customHeight="1">
-      <c r="A124" s="39" t="s">
+      <c r="A124" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="B124" s="39"/>
-      <c r="C124" s="39"/>
-      <c r="D124" s="39"/>
+      <c r="B124" s="35"/>
+      <c r="C124" s="35"/>
+      <c r="D124" s="35"/>
       <c r="E124" s="12" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="125" spans="1:6">
-      <c r="A125" s="35" t="s">
+      <c r="A125" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="B125" s="36"/>
-      <c r="C125" s="36"/>
-      <c r="D125" s="37"/>
+      <c r="B125" s="26"/>
+      <c r="C125" s="26"/>
+      <c r="D125" s="27"/>
       <c r="E125" s="15" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="31.2">
-      <c r="A126" s="35" t="s">
+      <c r="A126" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="37"/>
+      <c r="B126" s="26"/>
+      <c r="C126" s="26"/>
+      <c r="D126" s="27"/>
       <c r="E126" s="12" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="31.2">
-      <c r="A127" s="35" t="s">
+      <c r="A127" s="25" t="s">
         <v>273</v>
       </c>
-      <c r="B127" s="36"/>
-      <c r="C127" s="36"/>
-      <c r="D127" s="37"/>
+      <c r="B127" s="26"/>
+      <c r="C127" s="26"/>
+      <c r="D127" s="27"/>
       <c r="E127" s="12" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="31.2">
-      <c r="A128" s="35" t="s">
+      <c r="A128" s="25" t="s">
         <v>275</v>
       </c>
-      <c r="B128" s="36"/>
-      <c r="C128" s="36"/>
-      <c r="D128" s="37"/>
+      <c r="B128" s="26"/>
+      <c r="C128" s="26"/>
+      <c r="D128" s="27"/>
       <c r="E128" s="12" t="s">
         <v>276</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A84:A96"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A14:A22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A25:A27"/>
     <mergeCell ref="A128:D128"/>
     <mergeCell ref="A28:A40"/>
     <mergeCell ref="A11:C11"/>
@@ -3809,20 +3830,6 @@
     <mergeCell ref="A56:A65"/>
     <mergeCell ref="A66:A69"/>
     <mergeCell ref="A70:A83"/>
-    <mergeCell ref="A84:A96"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A14:A22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="D84:D86 D86:E104 E117:E119 D117:D120 D105 D106:E116 D14:E69 D70:D73 D74:E79 D80:D81 D82:E83">
     <cfRule type="expression" dxfId="14" priority="14">
